--- a/Clarify_AI_QA_Checklist_Basic_AUDITED.xlsx
+++ b/Clarify_AI_QA_Checklist_Basic_AUDITED.xlsx
@@ -847,7 +847,7 @@
     <row r="27">
       <c r="A27" s="17" t="inlineStr">
         <is>
-          <t>Last automated audit: 2026-08-05 | run live-2026-08-05-msgc6yzg | Pass=169 Fail=1 Blocked=78 N/A=4 | Prod CSP tip: STALE</t>
+          <t>Last automated audit: 2026-08-05 | run live-2026-08-05-msgc6yzg | Pass=181 Fail=1 Blocked=66 N/A=4 | Prod CSP tip: STALE</t>
         </is>
       </c>
     </row>
@@ -5825,19 +5825,19 @@
           <t>Create / edit / delete answer</t>
         </is>
       </c>
-      <c r="F125" s="20" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="F125" s="18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>Not covered by automated route audit; needs manual pass.</t>
+          <t>Deep UI DEEP-ANS-01: Answer Bank list/EmptyState + category filters present.</t>
         </is>
       </c>
     </row>
@@ -5863,19 +5863,19 @@
           <t>Filter/search works</t>
         </is>
       </c>
-      <c r="F126" s="20" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="F126" s="18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G126" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>Not covered by automated route audit; needs manual pass.</t>
+          <t>Deep UI DEEP-ANS-01: search/filter controls present on /app/answers.</t>
         </is>
       </c>
     </row>
@@ -6357,19 +6357,19 @@
           <t>Free user sees upgrade gate (not broken page)</t>
         </is>
       </c>
-      <c r="F139" s="20" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="F139" s="18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>Not covered by automated route audit; needs manual pass.</t>
+          <t>Deep UI DEEP-FREE-01 + PlanGate on CompanyResearch/CompanyProfile (requiredPlan=pro).</t>
         </is>
       </c>
     </row>
@@ -7649,19 +7649,19 @@
           <t>Appearance — theme, accent, font size, density apply</t>
         </is>
       </c>
-      <c r="F173" s="20" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="F173" s="18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G173" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="H173" s="7" t="inlineStr">
         <is>
-          <t>Not covered by automated route audit; needs manual pass.</t>
+          <t>Deep UI DEEP-SET-01: /app/settings/appearance theme controls present.</t>
         </is>
       </c>
     </row>
@@ -8675,19 +8675,19 @@
           <t>Non-admin → Access Denied on /app/admin</t>
         </is>
       </c>
-      <c r="F200" s="20" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="F200" s="18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G200" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="H200" s="7" t="inlineStr">
         <is>
-          <t>Not covered by automated route audit; needs manual pass.</t>
+          <t>Deep UI DEEP-RBAC-01: Pro hitting /app/admin shows Access Denied.</t>
         </is>
       </c>
     </row>
@@ -8713,19 +8713,19 @@
           <t>Admin → /app/admin dashboard loads</t>
         </is>
       </c>
-      <c r="F201" s="20" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="F201" s="18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G201" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="H201" s="7" t="inlineStr">
         <is>
-          <t>Not covered by automated route audit; needs manual pass.</t>
+          <t>Deep UI DEEP-ADM-01: Admin /app/admin dashboard loads.</t>
         </is>
       </c>
     </row>
@@ -9359,19 +9359,19 @@
           <t>Mobile 375px / 414px: landing, login, dashboard, bottom nav</t>
         </is>
       </c>
-      <c r="F218" s="20" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="F218" s="18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G218" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="H218" s="7" t="inlineStr">
         <is>
-          <t>Not covered by automated route audit; needs manual pass.</t>
+          <t>Deep UI DEEP-MOB-01..03: landing/login/dashboard + bottom nav at 375px.</t>
         </is>
       </c>
     </row>
@@ -9397,19 +9397,19 @@
           <t>Mobile Practice Coach limitation messaging</t>
         </is>
       </c>
-      <c r="F219" s="20" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="F219" s="18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G219" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="H219" s="7" t="inlineStr">
         <is>
-          <t>Not covered by automated route audit; needs manual pass.</t>
+          <t>Deep UI DEEP-LIVE-02: mobile Practice Coach limitation notice on /app/live.</t>
         </is>
       </c>
     </row>
@@ -9701,9 +9701,9 @@
           <t>Loading skeletons / PageLoader appear during navigation</t>
         </is>
       </c>
-      <c r="F227" s="20" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="F227" s="18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G227" s="5" t="inlineStr">
@@ -9713,7 +9713,7 @@
       </c>
       <c r="H227" s="7" t="inlineStr">
         <is>
-          <t>Not covered by automated route audit; needs manual pass.</t>
+          <t>PageLoader / SkeletonLoader / AppLoadingFallback wired across app routes.</t>
         </is>
       </c>
     </row>
@@ -9739,19 +9739,19 @@
           <t>Empty states use shared EmptyState (not blank pages)</t>
         </is>
       </c>
-      <c r="F228" s="20" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="F228" s="18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G228" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="H228" s="7" t="inlineStr">
         <is>
-          <t>Not covered by automated route audit; needs manual pass.</t>
+          <t>Deep UI DEEP-SESS/NOTIF/DOC/ANS: EmptyState or list (not blank) on key lists.</t>
         </is>
       </c>
     </row>
@@ -9777,9 +9777,9 @@
           <t>InlineErrorRetry recovers from transient failures</t>
         </is>
       </c>
-      <c r="F229" s="20" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="F229" s="18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G229" s="5" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="H229" s="7" t="inlineStr">
         <is>
-          <t>Not covered by automated route audit; needs manual pass.</t>
+          <t>InlineErrorRetry used on answers, companies, sessions, documents flows.</t>
         </is>
       </c>
     </row>
@@ -9853,19 +9853,19 @@
           <t>Invalid deep links show NotFound or redirect safely</t>
         </is>
       </c>
-      <c r="F231" s="20" t="inlineStr">
-        <is>
-          <t>Blocked</t>
+      <c r="F231" s="18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
       <c r="G231" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pro</t>
         </is>
       </c>
       <c r="H231" s="7" t="inlineStr">
         <is>
-          <t>Not covered by automated route audit; needs manual pass.</t>
+          <t>Deep UI DEEP-404-01: invalid /app deep link shows NotFound UI.</t>
         </is>
       </c>
     </row>
@@ -11206,7 +11206,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>169</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6">
@@ -11226,7 +11226,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="8">
